--- a/output/(山本)規範適合性_記法適合性_再構成.xlsx
+++ b/output/(山本)規範適合性_記法適合性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,146 +461,96 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>文書内で定義されたスタイルガイドやプロジェクト規定に基づき、各階層の箇条書き記号（中黒、番号、記号等）が、文書全体で統一して適用されている。</t>
+          <t>箇条書きの各項目において、階層構造をインデントで明示し、文末表現（名詞止め、動詞終止形など）をプロジェクトの記述標準またはスタイルガイドに準拠して統一している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】第1章では「・」を使用し、第2章では「-」を箇条書きの文頭記号として使用している。（章ごとに記号が混在している）
-→【適合例】全ての章において、第1レベルの箇条書き記号を「・」で統一している。</t>
+【非適合例】エラー発生時の処理：
+- ログを出力する。
+- 管理者へのメール通知
+- DBロールバック処理を行う。（文末の品詞が混在しており、読み手の負担となる。）
+→【適合例】エラー発生時の処理：
+- エラーログを出力する。
+- 管理者にメールを通知する。
+- DBのロールバック処理を行う。（すべての項目の文末を動詞の終止形で統一している。）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>箇条書きのルールに適合している</t>
+          <t>図表の記載ルールに適合している</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>同一の箇条書きリスト内において、末尾の表現形式（体言止め、または句点付きの文章）が整合しており、論理的な粒度が揃っている。</t>
+          <t>すべての図表に本文から参照可能な一意の図表番号およびタイトルを付与し、そのタイトルが図表の内容と矛盾なく一致している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】・データの入力
-・ファイルを削除する。（体言止めと終止形が混在している）
-→【適合例】・データの入力
-・ファイルの削除</t>
+【非適合例】図2-1：システム全体構成図（実際にはログイン処理のシーケンス図が描画されており、タイトルと内容が一致していない。）
+→【適合例】図2-1：ログイン処理シーケンス図（ログイン処理のシーケンス図が描画されており、本文の「詳細は図2-1を参照」という記述と矛盾なく対応している。）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>図表の記載ルールに適合している</t>
+          <t>各種の記法（状態遷移表，UMLなど）に則している</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>全ての図表に対して、一連の通し番号と内容を簡潔に示す名称（タイトル）が、規定の配置場所（図の下部、表の上部等）に漏れなく付与されている。</t>
+          <t>UML標準規格に基づき、矢印の形状による同期および非同期の区別やステレオタイプなどの構成要素を、規定の記法に従って記述している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】図.（タイトルが記載されておらず、番号のみとなっている）
-→【適合例】図3-1 ネットワーク構成図</t>
+          <t>★新規追加
+【非適合例】非同期のメッセージ送信を、同期メッセージと同じ黒塗りの三角矢印で描画している。（UMLの記法に違反しており、処理のブロック状態を誤認させる原因となる。）
+→【適合例】非同期のメッセージ送信を、開いた矢印を用いて規定の記法に則って図示している。（同期および非同期の区別が明確になり、設計意図が正確に伝わる。）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>図表の記載ルールに適合している</t>
+          <t>各種の記法（状態遷移表，UMLなど）に則している</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>図表のタイトルおよび図中の構成要素（ラベル、データ、凡例等）が、本文の説明文や外部設計等の定義内容と完全に一致しており、矛盾が生じていない。</t>
+          <t>状態遷移表の記述ルールに基づき、現在の状態に対するトリガー、ガード条件、および次状態への遷移を表形式で網羅的に記述している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】図2-1 ログインフローという名称だが、図の中身はログアウト処理の遷移図になっている。（タイトルと内容が一致していない）
-→【適合例】図2-1 ログインフローという名称の通り、ログイン処理の画面遷移図が掲載されている。</t>
+          <t>★新規追加
+【非適合例】状態遷移表において、イベント発生時の「ガード条件」の列を省略している。（条件分岐の仕様が欠落しており、実装時の判断基準が不明確になる。）
+→【適合例】状態遷移表において、「現在の状態」「イベント」「ガード条件」「次状態」「アクション」の各列を網羅的に記述している。（遷移条件が明確になり、設計の網羅性を担保している。）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>各種の記法（状態遷移表，UMLなど）に則している</t>
+          <t>用字用語が正しい</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>状態遷移図や状態遷移表において、遷移を誘発するイベントと実行されるアクションが、定義された記法（区切り文字や記述順序等）に従い、網羅的に記述されている。</t>
+          <t>プロジェクトの用語定義集や執筆規約に準拠し、誤字、脱字、および同音異義語の誤変換を排除して記述している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】状態Aから状態Bへ矢印のみが引かれ、遷移条件が記述されていない。（記法に従わず内容が理解しにくい）
-→【適合例】「ボタン押下/画面更新」のように、イベントとアクションを規定のセパレータで区切り記述している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>各種の記法（状態遷移表，UMLなど）に則している</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>UML（クラス図、シーケンス図等）において、要素間の関係性（継承、実現、依存、関連等）を示す線や矢印の形状が、OMG等の標準記法の定義に基づき厳格に使い分けられている。</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】クラス図において、継承関係と関連の線をすべて同じ実線の矢印で描画している。（UMLの記法に則っていない）
-→【適合例】継承には白抜きの三角矢印、関連には通常の実線矢印を用いている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>用字用語が正しい</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>変換ミス、タイピングミスによる誤字、および格助詞の欠落や重複といった脱字を排除し、正確な日本語で記述されている。</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>【非適合例】「作成した機能をデスとして実行する」（「テスト」が「デス」になっている誤字）
-→【適合例】「作成した機能をテストとして実行する」</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>用字用語が正しい</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>プロジェクト指定の用語集、または公用文の表記ルール（送り仮名の付け方等）に基づき、表記揺れのない語彙を文書全体で一貫して選択している。</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】同一文書内で「サーバ」と「サーバー」の表記が混在している。（表記揺れが発生している）
-→【適合例】プロジェクトの用語定義に従い「サーバ」という表記に統一している。</t>
+【非適合例】データの以降処理において、以上系のテストケースを実施する。（「移行」および「異常」の同音異義語による誤変換が含まれている。）
+→【適合例】データの移行処理において、異常系のテストケースを実施する。（文脈に応じた正しい漢字を使用している。）</t>
         </is>
       </c>
     </row>
